--- a/docs/data/jp/xlsx/5388.xlsx
+++ b/docs/data/jp/xlsx/5388.xlsx
@@ -9264,7 +9264,7 @@
     <row r="110">
       <c r="A110" s="18" t="inlineStr">
         <is>
-          <t>Gain On Sales Of Securities NOI</t>
+          <t>유가증권 매각 이익</t>
         </is>
       </c>
       <c r="C110" s="20" t="n">
@@ -9584,7 +9584,7 @@
     <row r="117">
       <c r="A117" s="18" t="inlineStr">
         <is>
-          <t>Loss Due To Spoilage NOE</t>
+          <t>공손비</t>
         </is>
       </c>
       <c r="D117" s="20" t="n">
@@ -9641,7 +9641,7 @@
     <row r="120">
       <c r="A120" s="18" t="inlineStr">
         <is>
-          <t>Settlement Money NOE</t>
+          <t>해결금</t>
         </is>
       </c>
       <c r="I120" s="20" t="n">
@@ -14100,7 +14100,7 @@
     <row r="215">
       <c r="A215" s="18" t="inlineStr">
         <is>
-          <t>Increase Decrease In Provision For Mine Closure Expenses Ope CF</t>
+          <t>폐광 비용 충당금 증감액(△는 감소)</t>
         </is>
       </c>
       <c r="D215" s="20" t="n">
@@ -20450,7 +20450,7 @@
     <row r="136">
       <c r="A136" s="18" t="inlineStr">
         <is>
-          <t>Provision For Mine Closure Expenses NCL</t>
+          <t>폐광 비용 충당금</t>
         </is>
       </c>
       <c r="C136" s="20" t="n">
@@ -20574,7 +20574,7 @@
     <row r="140">
       <c r="A140" s="18" t="inlineStr">
         <is>
-          <t>Long Term Accounts Payable Facilities</t>
+          <t>장기 설비 관련 미지급금</t>
         </is>
       </c>
       <c r="E140" s="20" t="n">
@@ -20859,7 +20859,7 @@
     <row r="149">
       <c r="A149" s="18" t="inlineStr">
         <is>
-          <t>Reserve For Dividends3</t>
+          <t>배당 준비 적립금</t>
         </is>
       </c>
       <c r="E149" s="20" t="n">
@@ -20884,7 +20884,7 @@
     <row r="150">
       <c r="A150" s="18" t="inlineStr">
         <is>
-          <t>Reserve For Research And Development</t>
+          <t>연구개발 적립금</t>
         </is>
       </c>
       <c r="E150" s="20" t="n">
@@ -20909,7 +20909,7 @@
     <row r="151">
       <c r="A151" s="18" t="inlineStr">
         <is>
-          <t>Reserve For Resource Development</t>
+          <t>자원개발 적립금</t>
         </is>
       </c>
       <c r="E151" s="20" t="n">
